--- a/exit_survey_cleaned.xlsx
+++ b/exit_survey_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\Documents\Project\Rebound Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0986580E-5789-41F1-80F0-D94C6174FC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD42A3E-969B-490A-8C8B-CD7FDD2E6B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -982,6 +982,7 @@
   <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="54.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="43.26953125" customWidth="1"/>
